--- a/data/dividends_info_20260419.xlsx
+++ b/data/dividends_info_20260419.xlsx
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>28.60000038146973</v>
+        <v>28.35000038146973</v>
       </c>
       <c r="I40" t="n">
-        <v>3.881118829352121</v>
+        <v>3.915343862660136</v>
       </c>
       <c r="J40" t="n">
         <v>46</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>16.53000068664551</v>
+        <v>16.40999984741211</v>
       </c>
       <c r="I70" t="n">
-        <v>1.814881957278854</v>
+        <v>1.828153581898483</v>
       </c>
       <c r="J70" t="n">
         <v>29</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>21.29999923706055</v>
+        <v>20.70000076293945</v>
       </c>
       <c r="I99" t="n">
-        <v>3.286385094240039</v>
+        <v>3.381642387440174</v>
       </c>
       <c r="J99" t="n">
         <v>29</v>
@@ -5457,8 +5457,12 @@
           <t>IT0005495657</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
+      <c r="H107" t="n">
+        <v>3.872999906539917</v>
+      </c>
+      <c r="I107" t="n">
+        <v>4.389362357405156</v>
+      </c>
       <c r="J107" t="n">
         <v>29</v>
       </c>
@@ -5923,8 +5927,12 @@
           <t>IT0005573065</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
+      <c r="H117" t="n">
+        <v>2.869999885559082</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.3484320696428174</v>
+      </c>
       <c r="J117" t="n">
         <v>29</v>
       </c>
@@ -8716,7 +8724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C640"/>
+  <dimension ref="A1:C600"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10184,7 +10192,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -10201,7 +10209,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -10218,7 +10226,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10228,14 +10236,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>B.F. S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10245,14 +10253,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10262,14 +10270,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10279,14 +10287,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10303,7 +10311,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10313,14 +10321,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>B.F. S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10330,14 +10338,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10347,14 +10355,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>NEXT RE SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10364,14 +10372,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10388,7 +10396,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10405,7 +10413,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10422,7 +10430,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10439,7 +10447,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10473,7 +10481,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10490,7 +10498,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10507,7 +10515,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10524,7 +10532,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10541,7 +10549,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10558,7 +10566,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10575,7 +10583,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10592,7 +10600,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10609,7 +10617,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10626,7 +10634,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10643,7 +10651,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10653,14 +10661,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10670,14 +10678,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10694,7 +10702,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10711,7 +10719,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10728,7 +10736,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10745,12 +10753,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -10762,12 +10770,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -10779,29 +10787,29 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -10813,12 +10821,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -10830,46 +10838,46 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -10881,12 +10889,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -10898,12 +10906,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -10915,7 +10923,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10932,7 +10940,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10949,7 +10957,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10966,7 +10974,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10983,7 +10991,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11000,7 +11008,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11017,7 +11025,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11034,7 +11042,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11051,7 +11059,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11061,14 +11069,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11085,7 +11093,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11102,7 +11110,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11119,7 +11127,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11129,14 +11137,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11153,7 +11161,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11170,7 +11178,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11187,7 +11195,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11204,7 +11212,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11221,7 +11229,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11238,7 +11246,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11248,14 +11256,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11272,7 +11280,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11289,7 +11297,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11306,7 +11314,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11323,7 +11331,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11340,7 +11348,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11357,7 +11365,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11367,14 +11375,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11384,14 +11392,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11408,7 +11416,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11425,7 +11433,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11459,7 +11467,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11476,7 +11484,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11493,7 +11501,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11510,7 +11518,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11527,7 +11535,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11537,14 +11545,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11561,7 +11569,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11578,7 +11586,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11588,14 +11596,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11612,7 +11620,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11629,7 +11637,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11646,7 +11654,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11663,12 +11671,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11680,29 +11688,29 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11714,46 +11722,46 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11765,12 +11773,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11782,12 +11790,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11799,29 +11807,29 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11833,7 +11841,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11850,7 +11858,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11860,14 +11868,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11884,7 +11892,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11901,7 +11909,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11918,7 +11926,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11935,7 +11943,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11952,7 +11960,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -11969,7 +11977,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -11986,7 +11994,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -11996,14 +12004,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12020,7 +12028,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12037,7 +12045,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12054,7 +12062,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12071,7 +12079,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12088,7 +12096,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12105,7 +12113,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12122,7 +12130,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12139,7 +12147,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12156,7 +12164,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12173,7 +12181,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12190,7 +12198,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12207,7 +12215,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12224,7 +12232,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12241,7 +12249,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12251,14 +12259,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12275,7 +12283,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12292,7 +12300,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -12309,7 +12317,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -12326,7 +12334,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -12343,7 +12351,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12360,7 +12368,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -12377,7 +12385,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -12394,7 +12402,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12411,7 +12419,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -12428,7 +12436,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -12445,7 +12453,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -12462,7 +12470,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -12472,14 +12480,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -12489,14 +12497,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -12513,7 +12521,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -12530,7 +12538,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -12547,7 +12555,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -12564,7 +12572,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -12574,14 +12582,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -12598,7 +12606,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -12608,14 +12616,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -12625,14 +12633,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -12649,7 +12657,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -12666,7 +12674,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -12683,7 +12691,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -12700,7 +12708,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -12717,7 +12725,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -12727,14 +12735,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -12751,7 +12759,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -12768,7 +12776,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -12785,7 +12793,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -12802,7 +12810,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -12819,7 +12827,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -12836,7 +12844,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -12853,7 +12861,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -12870,7 +12878,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -12887,7 +12895,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -12904,7 +12912,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -12921,7 +12929,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -12938,7 +12946,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -12955,7 +12963,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -12965,14 +12973,14 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -12989,7 +12997,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -13006,7 +13014,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -13023,7 +13031,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -13040,7 +13048,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -13050,14 +13058,14 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -13074,7 +13082,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -13091,7 +13099,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -13108,7 +13116,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -13125,7 +13133,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -13142,7 +13150,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -13152,14 +13160,14 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -13169,14 +13177,14 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -13193,7 +13201,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -13210,12 +13218,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -13227,12 +13235,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -13244,12 +13252,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -13261,29 +13269,29 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -13295,80 +13303,80 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -13380,7 +13388,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -13397,7 +13405,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -13414,7 +13422,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -13431,7 +13439,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -13441,14 +13449,14 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -13465,7 +13473,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -13482,7 +13490,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -13499,7 +13507,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -13516,7 +13524,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -13526,14 +13534,14 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -13550,7 +13558,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -13567,7 +13575,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -13584,7 +13592,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -13601,7 +13609,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -13618,7 +13626,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -13635,7 +13643,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -13652,7 +13660,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -13669,7 +13677,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -13686,7 +13694,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -13703,7 +13711,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -13720,7 +13728,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -13737,7 +13745,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -13754,7 +13762,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -13771,7 +13779,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -13781,14 +13789,14 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -13805,7 +13813,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -13822,7 +13830,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -13839,7 +13847,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -13849,14 +13857,14 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -13873,7 +13881,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -13890,7 +13898,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -13907,7 +13915,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -13924,7 +13932,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -13941,7 +13949,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -13958,7 +13966,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -13975,7 +13983,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -13992,7 +14000,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -14009,7 +14017,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -14019,14 +14027,14 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -14036,14 +14044,14 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -14060,7 +14068,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -14077,7 +14085,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -14094,7 +14102,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -14111,7 +14119,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -14128,7 +14136,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -14145,7 +14153,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -14162,7 +14170,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -14179,7 +14187,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -14196,7 +14204,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -14206,14 +14214,14 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -14230,7 +14238,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -14247,7 +14255,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -14257,14 +14265,14 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -14281,7 +14289,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -14291,14 +14299,14 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -14315,7 +14323,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -14325,14 +14333,14 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -14349,7 +14357,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -14359,14 +14367,14 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -14383,7 +14391,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -14400,7 +14408,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -14417,7 +14425,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -14434,7 +14442,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -14451,12 +14459,12 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -14468,12 +14476,12 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -14485,12 +14493,12 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -14502,12 +14510,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -14519,46 +14527,46 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -14570,12 +14578,12 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -14587,29 +14595,29 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -14621,97 +14629,97 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -14723,12 +14731,12 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -14740,29 +14748,29 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -14774,29 +14782,29 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -14808,7 +14816,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -14825,46 +14833,46 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -14876,29 +14884,29 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -14910,29 +14918,29 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -14944,63 +14952,63 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -15012,46 +15020,46 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -15063,29 +15071,29 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -15097,12 +15105,12 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -15114,46 +15122,46 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -15165,7 +15173,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -15175,14 +15183,14 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -15199,7 +15207,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -15209,14 +15217,14 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -15226,7 +15234,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -15267,7 +15275,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -15277,53 +15285,53 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -15335,29 +15343,29 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -15369,29 +15377,29 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -15403,12 +15411,12 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -15420,80 +15428,80 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -15505,29 +15513,29 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -15539,12 +15547,12 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -15556,46 +15564,46 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -15607,12 +15615,12 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -15624,7 +15632,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -15634,14 +15642,14 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -15658,7 +15666,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -15668,14 +15676,14 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -15685,14 +15693,14 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -15702,19 +15710,19 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -15726,63 +15734,63 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -15794,80 +15802,80 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -15879,29 +15887,29 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -15913,12 +15921,12 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -15930,12 +15938,12 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -15947,46 +15955,46 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -15998,29 +16006,29 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -16032,12 +16040,12 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -16049,7 +16057,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -16059,14 +16067,14 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -16076,14 +16084,14 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -16093,14 +16101,14 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -16110,14 +16118,14 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -16127,14 +16135,14 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -16151,7 +16159,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -16161,14 +16169,14 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -16202,7 +16210,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -16212,14 +16220,14 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -16229,14 +16237,14 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -16246,14 +16254,14 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -16263,14 +16271,14 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -16287,7 +16295,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -16297,87 +16305,87 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -16389,12 +16397,12 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -16406,29 +16414,29 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -16440,63 +16448,63 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -16508,80 +16516,80 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -16593,63 +16601,63 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -16661,29 +16669,29 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -16695,12 +16703,12 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -16712,97 +16720,97 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -16814,97 +16822,97 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -16916,80 +16924,80 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -17001,12 +17009,12 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -17018,12 +17026,12 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -17035,46 +17043,46 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -17086,12 +17094,12 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -17103,12 +17111,12 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -17120,29 +17128,29 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -17154,12 +17162,12 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -17171,29 +17179,29 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>TENARIS S.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -17205,12 +17213,12 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -17222,12 +17230,12 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -17239,12 +17247,12 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -17256,46 +17264,46 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -17307,29 +17315,29 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -17341,63 +17349,63 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -17409,80 +17417,80 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -17494,12 +17502,12 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -17511,29 +17519,29 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -17545,29 +17553,29 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -17579,63 +17587,63 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -17647,12 +17655,12 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -17664,29 +17672,29 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -17698,12 +17706,12 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -17720,7 +17728,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -17732,12 +17740,12 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -17749,46 +17757,46 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -17800,29 +17808,29 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -17834,12 +17842,12 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -17851,29 +17859,29 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -17885,12 +17893,12 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -17902,63 +17910,63 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -17970,12 +17978,12 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -17987,63 +17995,63 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -18055,46 +18063,46 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -18106,29 +18114,29 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -18140,12 +18148,12 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -18157,12 +18165,12 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -18174,12 +18182,12 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -18191,29 +18199,29 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -18225,12 +18233,12 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -18242,7 +18250,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -18259,7 +18267,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -18269,14 +18277,14 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -18286,14 +18294,14 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -18310,7 +18318,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -18320,14 +18328,14 @@
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -18344,7 +18352,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -18361,7 +18369,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -18378,7 +18386,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -18395,7 +18403,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -18412,7 +18420,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -18429,46 +18437,46 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -18480,12 +18488,12 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -18497,29 +18505,29 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -18531,29 +18539,29 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -18565,12 +18573,12 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -18582,80 +18590,80 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -18667,29 +18675,29 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -18701,29 +18709,29 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>VINCENZO ZUCCHI S.p.A.</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -18735,12 +18743,12 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -18752,29 +18760,29 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -18786,12 +18794,12 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -18803,63 +18811,63 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -18871,12 +18879,12 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -18888,712 +18896,32 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Officina Stellare S.p.A.</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="601">
-      <c r="A601" t="inlineStr">
-        <is>
-          <t>F.I.L.A. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B601" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="C601" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="602">
-      <c r="A602" t="inlineStr">
-        <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B602" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="C602" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="603">
-      <c r="A603" t="inlineStr">
-        <is>
-          <t>First Capital S.p.A.</t>
-        </is>
-      </c>
-      <c r="B603" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="C603" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="604">
-      <c r="A604" t="inlineStr">
-        <is>
-          <t>ENAV S.p.A.</t>
-        </is>
-      </c>
-      <c r="B604" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="C604" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="605">
-      <c r="A605" t="inlineStr">
-        <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
-        </is>
-      </c>
-      <c r="B605" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="C605" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="606">
-      <c r="A606" t="inlineStr">
-        <is>
-          <t>EUROTECH S.p.A.</t>
-        </is>
-      </c>
-      <c r="B606" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="C606" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="607">
-      <c r="A607" t="inlineStr">
-        <is>
-          <t>BIESSE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B607" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="C607" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="608">
-      <c r="A608" t="inlineStr">
-        <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B608" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="C608" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="609">
-      <c r="A609" t="inlineStr">
-        <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
-        </is>
-      </c>
-      <c r="B609" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="C609" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="610">
-      <c r="A610" t="inlineStr">
-        <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B610" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="C610" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="611">
-      <c r="A611" t="inlineStr">
-        <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
-        </is>
-      </c>
-      <c r="B611" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="C611" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="612">
-      <c r="A612" t="inlineStr">
-        <is>
-          <t>FIDIA S.p.A</t>
-        </is>
-      </c>
-      <c r="B612" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C612" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="613">
-      <c r="A613" t="inlineStr">
-        <is>
-          <t>ERG S.p.A.</t>
-        </is>
-      </c>
-      <c r="B613" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C613" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="614">
-      <c r="A614" t="inlineStr">
-        <is>
-          <t>ECOSUNTEK S.p.A.</t>
-        </is>
-      </c>
-      <c r="B614" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C614" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="615">
-      <c r="A615" t="inlineStr">
-        <is>
-          <t>ERG S.p.A.</t>
-        </is>
-      </c>
-      <c r="B615" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C615" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="616">
-      <c r="A616" t="inlineStr">
-        <is>
-          <t>EL.EN. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B616" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C616" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="617">
-      <c r="A617" t="inlineStr">
-        <is>
-          <t>CY4Gate S.p.A.</t>
-        </is>
-      </c>
-      <c r="B617" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C617" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="618">
-      <c r="A618" t="inlineStr">
-        <is>
-          <t>GVS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B618" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C618" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="619">
-      <c r="A619" t="inlineStr">
-        <is>
-          <t>CLABO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B619" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C619" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="620">
-      <c r="A620" t="inlineStr">
-        <is>
-          <t>IRCE s.p.a</t>
-        </is>
-      </c>
-      <c r="B620" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C620" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="621">
-      <c r="A621" t="inlineStr">
-        <is>
-          <t>MARR S.p.A.</t>
-        </is>
-      </c>
-      <c r="B621" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C621" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="622">
-      <c r="A622" t="inlineStr">
-        <is>
-          <t>VINCENZO ZUCCHI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B622" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C622" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="623">
-      <c r="A623" t="inlineStr">
-        <is>
-          <t>VNE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B623" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C623" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="624">
-      <c r="A624" t="inlineStr">
-        <is>
-          <t>CLASS EDITORI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B624" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C624" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="625">
-      <c r="A625" t="inlineStr">
-        <is>
-          <t>MARR S.p.A.</t>
-        </is>
-      </c>
-      <c r="B625" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C625" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="626">
-      <c r="A626" t="inlineStr">
-        <is>
-          <t>REPLY S.p.A.</t>
-        </is>
-      </c>
-      <c r="B626" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C626" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="627">
-      <c r="A627" t="inlineStr">
-        <is>
-          <t>VNE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B627" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C627" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="628">
-      <c r="A628" t="inlineStr">
-        <is>
-          <t>SOGES GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B628" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C628" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="629">
-      <c r="A629" t="inlineStr">
-        <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B629" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C629" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="630">
-      <c r="A630" t="inlineStr">
-        <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B630" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C630" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="631">
-      <c r="A631" t="inlineStr">
-        <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B631" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C631" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="632">
-      <c r="A632" t="inlineStr">
-        <is>
-          <t>Ferretti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B632" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C632" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="633">
-      <c r="A633" t="inlineStr">
-        <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B633" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C633" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="634">
-      <c r="A634" t="inlineStr">
-        <is>
-          <t>Renovalo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B634" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C634" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="635">
-      <c r="A635" t="inlineStr">
-        <is>
-          <t>OMER S.p.A.</t>
-        </is>
-      </c>
-      <c r="B635" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="C635" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="636">
-      <c r="A636" t="inlineStr">
-        <is>
-          <t>GREEN OLEO S.p.A</t>
-        </is>
-      </c>
-      <c r="B636" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="C636" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="637">
-      <c r="A637" t="inlineStr">
-        <is>
-          <t>EuroGroup Laminations S.p.A.</t>
-        </is>
-      </c>
-      <c r="B637" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="C637" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="638">
-      <c r="A638" t="inlineStr">
-        <is>
-          <t>BESTBE HOLDING S.p.A.</t>
-        </is>
-      </c>
-      <c r="B638" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="C638" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="639">
-      <c r="A639" t="inlineStr">
-        <is>
-          <t>Officina Stellare S.p.A.</t>
-        </is>
-      </c>
-      <c r="B639" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="C639" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="640">
-      <c r="A640" t="inlineStr">
-        <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B640" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="C640" t="inlineStr">
         <is>
           <t>Additional Periodic Financial Information</t>
         </is>
@@ -19623,61 +18951,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Officina Stellare S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>